--- a/Excel_MOD/_original.xlsx
+++ b/Excel_MOD/_original.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/drewfoster/Desktop/Excel_Automator/Excel-Automator/Excel_MOD/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Drew\PycharmProjects\Excel_MOD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC289E6A-7675-9B4C-B0AA-B3F1E9FB5AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB416D14-B817-4002-BBF7-B30445D1ACB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2355" yWindow="45" windowWidth="23250" windowHeight="15330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7849,7 +7849,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7881,6 +7881,12 @@
         <fgColor rgb="FF3366FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66FF66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -7894,7 +7900,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -8025,21 +8031,24 @@
     <xf numFmtId="169" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF424649"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF66FF66"/>
+      <color rgb="FF00FF00"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -8315,49 +8324,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AP489"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="26.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="30.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="31.1640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="35.1640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="27.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8485,7 +8494,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>1654</v>
       </c>
@@ -8607,7 +8616,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>1888</v>
       </c>
@@ -8729,7 +8738,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A4" s="27" t="s">
         <v>2573</v>
       </c>
@@ -8851,7 +8860,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A5" s="24" t="s">
         <v>2499</v>
       </c>
@@ -8971,7 +8980,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A6" s="24" t="s">
         <v>2559</v>
       </c>
@@ -9091,7 +9100,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="24" t="s">
         <v>2499</v>
       </c>
@@ -9213,7 +9222,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A8" s="24" t="s">
         <v>2559</v>
       </c>
@@ -9335,7 +9344,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>681</v>
       </c>
@@ -9457,7 +9466,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>732</v>
       </c>
@@ -9577,7 +9586,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A11" s="24" t="s">
         <v>1304</v>
       </c>
@@ -9697,7 +9706,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A12" s="24" t="s">
         <v>1341</v>
       </c>
@@ -9817,7 +9826,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A13" s="36" t="s">
         <v>1924</v>
       </c>
@@ -9939,7 +9948,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A14" s="27" t="s">
         <v>2274</v>
       </c>
@@ -10063,7 +10072,7 @@
         <v>2282</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
         <v>818</v>
       </c>
@@ -10183,7 +10192,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>829</v>
       </c>
@@ -10301,7 +10310,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A17" s="24" t="s">
         <v>2499</v>
       </c>
@@ -10423,7 +10432,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A18" s="24" t="s">
         <v>2559</v>
       </c>
@@ -10545,7 +10554,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A19" s="21" t="s">
         <v>1154</v>
       </c>
@@ -10661,7 +10670,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A20" s="21" t="s">
         <v>1154</v>
       </c>
@@ -10777,7 +10786,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
         <v>175</v>
       </c>
@@ -10897,7 +10906,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>221</v>
       </c>
@@ -11019,7 +11028,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
         <v>393</v>
       </c>
@@ -11141,7 +11150,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A24" s="24" t="s">
         <v>1150</v>
       </c>
@@ -11261,7 +11270,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>692</v>
       </c>
@@ -11381,7 +11390,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A26" s="24" t="s">
         <v>1157</v>
       </c>
@@ -11499,7 +11508,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A27" s="24" t="s">
         <v>1160</v>
       </c>
@@ -11617,7 +11626,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A28" s="24" t="s">
         <v>1239</v>
       </c>
@@ -11737,7 +11746,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A29" s="24" t="s">
         <v>1241</v>
       </c>
@@ -11857,7 +11866,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A30" s="24" t="s">
         <v>1243</v>
       </c>
@@ -11977,7 +11986,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A31" s="24" t="s">
         <v>1245</v>
       </c>
@@ -12095,7 +12104,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A32" s="24" t="s">
         <v>1247</v>
       </c>
@@ -12213,7 +12222,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A33" s="24" t="s">
         <v>1249</v>
       </c>
@@ -12331,7 +12340,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A34" s="24" t="s">
         <v>1251</v>
       </c>
@@ -12449,7 +12458,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A35" s="36" t="s">
         <v>1253</v>
       </c>
@@ -12569,7 +12578,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A36" s="24" t="s">
         <v>1261</v>
       </c>
@@ -12687,7 +12696,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A37" s="24" t="s">
         <v>1302</v>
       </c>
@@ -12807,7 +12816,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A38" s="24" t="s">
         <v>2219</v>
       </c>
@@ -12929,7 +12938,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A39" s="24" t="s">
         <v>2222</v>
       </c>
@@ -13049,7 +13058,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A40" s="24" t="s">
         <v>2226</v>
       </c>
@@ -13167,7 +13176,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A41" s="24" t="s">
         <v>2228</v>
       </c>
@@ -13285,7 +13294,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A42" s="24" t="s">
         <v>2230</v>
       </c>
@@ -13403,7 +13412,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="43" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A43" s="24" t="s">
         <v>2232</v>
       </c>
@@ -13521,7 +13530,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="44" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A44" s="24" t="s">
         <v>2234</v>
       </c>
@@ -13641,7 +13650,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="45" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A45" s="24" t="s">
         <v>2236</v>
       </c>
@@ -13761,7 +13770,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="46" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A46" s="24" t="s">
         <v>1046</v>
       </c>
@@ -13881,7 +13890,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="47" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A47" s="24" t="s">
         <v>1143</v>
       </c>
@@ -14001,7 +14010,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="48" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A48" s="24" t="s">
         <v>1146</v>
       </c>
@@ -14121,7 +14130,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="49" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A49" s="24" t="s">
         <v>1150</v>
       </c>
@@ -14241,7 +14250,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="50" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>213</v>
       </c>
@@ -14359,7 +14368,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="51" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A51" s="24" t="s">
         <v>1160</v>
       </c>
@@ -14477,7 +14486,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="52" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A52" s="24" t="s">
         <v>1166</v>
       </c>
@@ -14597,7 +14606,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="53" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A53" s="24" t="s">
         <v>1239</v>
       </c>
@@ -14717,7 +14726,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="54" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A54" s="24" t="s">
         <v>1241</v>
       </c>
@@ -14837,7 +14846,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="55" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A55" s="24" t="s">
         <v>1243</v>
       </c>
@@ -14957,7 +14966,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="56" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A56" s="24" t="s">
         <v>1245</v>
       </c>
@@ -15075,7 +15084,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="57" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A57" s="24" t="s">
         <v>1247</v>
       </c>
@@ -15193,7 +15202,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="58" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A58" s="24" t="s">
         <v>1251</v>
       </c>
@@ -15311,7 +15320,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="59" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A59" s="24" t="s">
         <v>1261</v>
       </c>
@@ -15429,7 +15438,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="60" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A60" s="24" t="s">
         <v>1292</v>
       </c>
@@ -15549,7 +15558,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="61" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A61" s="24" t="s">
         <v>1294</v>
       </c>
@@ -15667,7 +15676,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="62" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A62" s="24" t="s">
         <v>1296</v>
       </c>
@@ -15785,7 +15794,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="63" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A63" s="24" t="s">
         <v>1298</v>
       </c>
@@ -15903,7 +15912,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="64" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A64" s="24" t="s">
         <v>1300</v>
       </c>
@@ -16021,7 +16030,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="65" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A65" s="24" t="s">
         <v>1302</v>
       </c>
@@ -16141,7 +16150,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="66" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A66" s="24" t="s">
         <v>2222</v>
       </c>
@@ -16261,7 +16270,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="67" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A67" s="24" t="s">
         <v>2224</v>
       </c>
@@ -16381,7 +16390,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="68" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A68" s="24" t="s">
         <v>2226</v>
       </c>
@@ -16499,7 +16508,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="69" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A69" s="24" t="s">
         <v>2228</v>
       </c>
@@ -16617,7 +16626,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="70" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A70" s="24" t="s">
         <v>2230</v>
       </c>
@@ -16735,7 +16744,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="71" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A71" s="24" t="s">
         <v>2234</v>
       </c>
@@ -16855,7 +16864,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="72" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A72" s="24" t="s">
         <v>2236</v>
       </c>
@@ -16975,7 +16984,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="73" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A73" s="24" t="s">
         <v>1411</v>
       </c>
@@ -17097,7 +17106,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="74" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A74" s="36" t="s">
         <v>1675</v>
       </c>
@@ -17219,7 +17228,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="75" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A75" s="27" t="s">
         <v>1682</v>
       </c>
@@ -17341,7 +17350,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="76" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A76" s="36" t="s">
         <v>1958</v>
       </c>
@@ -17463,7 +17472,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="77" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A77" s="36" t="s">
         <v>2042</v>
       </c>
@@ -17585,7 +17594,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="78" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A78" s="36" t="s">
         <v>2086</v>
       </c>
@@ -17707,7 +17716,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="79" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A79" s="27" t="s">
         <v>2163</v>
       </c>
@@ -17829,7 +17838,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="80" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A80" s="24" t="s">
         <v>2452</v>
       </c>
@@ -17951,7 +17960,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="81" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A81" s="36" t="s">
         <v>2459</v>
       </c>
@@ -18073,7 +18082,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="82" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
         <v>256</v>
       </c>
@@ -18193,7 +18202,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="83" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A83" s="12" t="s">
         <v>312</v>
       </c>
@@ -18313,7 +18322,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="84" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
         <v>379</v>
       </c>
@@ -18431,7 +18440,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="85" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A85" s="12" t="s">
         <v>385</v>
       </c>
@@ -18549,7 +18558,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="86" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A86" s="24" t="s">
         <v>1411</v>
       </c>
@@ -18671,7 +18680,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="87" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A87" s="36" t="s">
         <v>1481</v>
       </c>
@@ -18793,7 +18802,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="88" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A88" s="36" t="s">
         <v>1508</v>
       </c>
@@ -18915,7 +18924,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="89" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A89" s="36" t="s">
         <v>1565</v>
       </c>
@@ -19037,7 +19046,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="90" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A90" s="24" t="s">
         <v>1411</v>
       </c>
@@ -19159,7 +19168,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="91" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A91" s="27" t="s">
         <v>1425</v>
       </c>
@@ -19283,7 +19292,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="92" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A92" s="36" t="s">
         <v>1432</v>
       </c>
@@ -19405,7 +19414,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="93" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A93" s="27" t="s">
         <v>1439</v>
       </c>
@@ -19527,7 +19536,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="94" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A94" s="27" t="s">
         <v>1488</v>
       </c>
@@ -19649,7 +19658,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="95" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A95" s="27" t="s">
         <v>1501</v>
       </c>
@@ -19771,7 +19780,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="96" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A96" s="27" t="s">
         <v>1515</v>
       </c>
@@ -19893,7 +19902,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="97" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A97" s="36" t="s">
         <v>1533</v>
       </c>
@@ -20015,7 +20024,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="98" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A98" s="27" t="s">
         <v>1585</v>
       </c>
@@ -20137,7 +20146,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="99" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A99" s="36" t="s">
         <v>1611</v>
       </c>
@@ -20259,7 +20268,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="100" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A100" s="36" t="s">
         <v>1635</v>
       </c>
@@ -20381,7 +20390,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="101" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A101" s="27" t="s">
         <v>1760</v>
       </c>
@@ -20503,7 +20512,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="102" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A102" s="36" t="s">
         <v>1811</v>
       </c>
@@ -20625,7 +20634,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="103" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A103" s="36" t="s">
         <v>1970</v>
       </c>
@@ -20747,7 +20756,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="104" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A104" s="27" t="s">
         <v>1989</v>
       </c>
@@ -20869,7 +20878,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="105" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A105" s="27" t="s">
         <v>2044</v>
       </c>
@@ -20991,7 +21000,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="106" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A106" s="27" t="s">
         <v>2092</v>
       </c>
@@ -21113,7 +21122,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="107" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A107" s="36" t="s">
         <v>2099</v>
       </c>
@@ -21235,7 +21244,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="108" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A108" s="36" t="s">
         <v>2247</v>
       </c>
@@ -21359,7 +21368,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="109" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A109" s="27" t="s">
         <v>2267</v>
       </c>
@@ -21481,7 +21490,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="110" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A110" s="36" t="s">
         <v>2349</v>
       </c>
@@ -21603,7 +21612,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="111" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A111" s="24" t="s">
         <v>2452</v>
       </c>
@@ -21725,7 +21734,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="112" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A112" s="27" t="s">
         <v>2520</v>
       </c>
@@ -21847,7 +21856,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="113" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A113" s="3" t="s">
         <v>448</v>
       </c>
@@ -21967,8 +21976,8 @@
         <v>97</v>
       </c>
     </row>
-    <row r="114" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="A114" s="12" t="s">
+    <row r="114" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A114" s="45" t="s">
         <v>455</v>
       </c>
       <c r="B114" s="13">
@@ -22087,8 +22096,8 @@
         <v>97</v>
       </c>
     </row>
-    <row r="115" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="A115" s="3" t="s">
+    <row r="115" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A115" s="45" t="s">
         <v>462</v>
       </c>
       <c r="B115" s="4">
@@ -22205,7 +22214,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="116" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A116" s="3" t="s">
         <v>468</v>
       </c>
@@ -22323,7 +22332,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="117" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A117" s="36" t="s">
         <v>1070</v>
       </c>
@@ -22439,8 +22448,8 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="118" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="A118" s="24" t="s">
+    <row r="118" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A118" s="44" t="s">
         <v>1090</v>
       </c>
       <c r="B118" s="35">
@@ -22555,7 +22564,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="119" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A119" s="24" t="s">
         <v>1223</v>
       </c>
@@ -22671,7 +22680,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="120" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A120" s="24" t="s">
         <v>1227</v>
       </c>
@@ -22787,7 +22796,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="121" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A121" s="24" t="s">
         <v>1233</v>
       </c>
@@ -22903,7 +22912,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="122" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A122" s="24" t="s">
         <v>1270</v>
       </c>
@@ -23019,7 +23028,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="123" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A123" s="27" t="s">
         <v>1521</v>
       </c>
@@ -23141,7 +23150,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="124" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A124" s="36" t="s">
         <v>1729</v>
       </c>
@@ -23263,7 +23272,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="125" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A125" s="36" t="s">
         <v>1900</v>
       </c>
@@ -23385,7 +23394,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="126" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A126" s="27" t="s">
         <v>1905</v>
       </c>
@@ -23509,7 +23518,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="127" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A127" s="36" t="s">
         <v>2028</v>
       </c>
@@ -23631,7 +23640,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="128" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A128" s="24" t="s">
         <v>2141</v>
       </c>
@@ -23747,7 +23756,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="129" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A129" s="24" t="s">
         <v>2143</v>
       </c>
@@ -23863,7 +23872,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="130" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A130" s="24" t="s">
         <v>2154</v>
       </c>
@@ -23979,7 +23988,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="131" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A131" s="24" t="s">
         <v>2158</v>
       </c>
@@ -24097,7 +24106,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="132" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A132" s="27" t="s">
         <v>2379</v>
       </c>
@@ -24219,7 +24228,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="133" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A133" s="24" t="s">
         <v>1090</v>
       </c>
@@ -24335,7 +24344,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="134" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A134" s="24" t="s">
         <v>1223</v>
       </c>
@@ -24451,7 +24460,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="135" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A135" s="24" t="s">
         <v>1227</v>
       </c>
@@ -24567,7 +24576,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="136" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A136" s="24" t="s">
         <v>1233</v>
       </c>
@@ -24683,7 +24692,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="137" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A137" s="36" t="s">
         <v>1453</v>
       </c>
@@ -24805,7 +24814,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="138" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A138" s="27" t="s">
         <v>1460</v>
       </c>
@@ -24927,7 +24936,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="139" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A139" s="36" t="s">
         <v>1661</v>
       </c>
@@ -25051,7 +25060,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="140" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A140" s="36" t="s">
         <v>1911</v>
       </c>
@@ -25173,7 +25182,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="141" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A141" s="27" t="s">
         <v>2169</v>
       </c>
@@ -25295,7 +25304,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="142" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A142" s="36" t="s">
         <v>2175</v>
       </c>
@@ -25417,7 +25426,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="143" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A143" s="3" t="s">
         <v>475</v>
       </c>
@@ -25537,7 +25546,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="144" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A144" s="27" t="s">
         <v>1279</v>
       </c>
@@ -25653,7 +25662,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="145" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A145" s="36" t="s">
         <v>1798</v>
       </c>
@@ -25775,7 +25784,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="146" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A146" s="27" t="s">
         <v>1850</v>
       </c>
@@ -25897,7 +25906,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="147" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A147" s="24" t="s">
         <v>2141</v>
       </c>
@@ -26013,7 +26022,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="148" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A148" s="24" t="s">
         <v>2143</v>
       </c>
@@ -26129,7 +26138,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="149" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A149" s="24" t="s">
         <v>2156</v>
       </c>
@@ -26245,7 +26254,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="150" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A150" s="24" t="s">
         <v>2158</v>
       </c>
@@ -26363,7 +26372,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="151" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A151" s="36" t="s">
         <v>2446</v>
       </c>
@@ -26485,7 +26494,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="152" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A152" s="24" t="s">
         <v>1343</v>
       </c>
@@ -26607,7 +26616,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="153" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A153" s="36" t="s">
         <v>1591</v>
       </c>
@@ -26729,7 +26738,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="154" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A154" s="27" t="s">
         <v>1604</v>
       </c>
@@ -26851,7 +26860,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="155" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A155" s="36" t="s">
         <v>1689</v>
       </c>
@@ -26973,7 +26982,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="156" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A156" s="27" t="s">
         <v>1716</v>
       </c>
@@ -27095,7 +27104,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="157" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A157" s="36" t="s">
         <v>1722</v>
       </c>
@@ -27217,7 +27226,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="158" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A158" s="36" t="s">
         <v>1734</v>
       </c>
@@ -27339,7 +27348,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="159" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A159" s="27" t="s">
         <v>1817</v>
       </c>
@@ -27461,7 +27470,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="160" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A160" s="36" t="s">
         <v>1837</v>
       </c>
@@ -27583,7 +27592,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="161" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A161" s="36" t="s">
         <v>1983</v>
       </c>
@@ -27705,7 +27714,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="162" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A162" s="36" t="s">
         <v>1996</v>
       </c>
@@ -27827,7 +27836,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="163" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A163" s="27" t="s">
         <v>2003</v>
       </c>
@@ -27949,7 +27958,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="164" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A164" s="36" t="s">
         <v>2010</v>
       </c>
@@ -28071,7 +28080,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="165" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A165" s="27" t="s">
         <v>2016</v>
       </c>
@@ -28193,7 +28202,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="166" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A166" s="36" t="s">
         <v>2051</v>
       </c>
@@ -28315,7 +28324,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="167" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A167" s="27" t="s">
         <v>2205</v>
       </c>
@@ -28437,7 +28446,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="168" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A168" s="36" t="s">
         <v>2212</v>
       </c>
@@ -28561,7 +28570,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="169" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A169" s="36" t="s">
         <v>2289</v>
       </c>
@@ -28683,7 +28692,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="170" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A170" s="36" t="s">
         <v>2309</v>
       </c>
@@ -28805,7 +28814,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="171" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A171" s="24" t="s">
         <v>2342</v>
       </c>
@@ -28927,7 +28936,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="172" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A172" s="36" t="s">
         <v>2513</v>
       </c>
@@ -29049,7 +29058,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="173" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A173" s="12" t="s">
         <v>490</v>
       </c>
@@ -29169,7 +29178,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="174" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A174" s="3" t="s">
         <v>507</v>
       </c>
@@ -29287,7 +29296,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="175" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A175" s="12" t="s">
         <v>513</v>
       </c>
@@ -29407,7 +29416,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="176" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A176" s="3" t="s">
         <v>613</v>
       </c>
@@ -29527,7 +29536,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="177" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A177" s="3" t="s">
         <v>627</v>
       </c>
@@ -29647,7 +29656,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="178" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A178" s="3" t="s">
         <v>635</v>
       </c>
@@ -29765,7 +29774,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="179" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A179" s="24" t="s">
         <v>1343</v>
       </c>
@@ -29887,7 +29896,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="180" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A180" s="36" t="s">
         <v>1494</v>
       </c>
@@ -30009,7 +30018,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="181" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A181" s="27" t="s">
         <v>1667</v>
       </c>
@@ -30131,7 +30140,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="182" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A182" s="36" t="s">
         <v>1710</v>
       </c>
@@ -30253,7 +30262,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="183" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A183" s="36" t="s">
         <v>1748</v>
       </c>
@@ -30375,7 +30384,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="184" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A184" s="36" t="s">
         <v>1775</v>
       </c>
@@ -30499,7 +30508,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="185" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A185" s="27" t="s">
         <v>1831</v>
       </c>
@@ -30621,7 +30630,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="186" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A186" s="27" t="s">
         <v>1964</v>
       </c>
@@ -30743,7 +30752,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="187" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A187" s="27" t="s">
         <v>1976</v>
       </c>
@@ -30865,7 +30874,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="188" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A188" s="36" t="s">
         <v>2283</v>
       </c>
@@ -30987,7 +30996,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="189" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A189" s="24" t="s">
         <v>2342</v>
       </c>
@@ -31109,7 +31118,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="190" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A190" s="27" t="s">
         <v>2418</v>
       </c>
@@ -31231,7 +31240,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="191" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A191" s="24" t="s">
         <v>1343</v>
       </c>
@@ -31353,7 +31362,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="192" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A192" s="36" t="s">
         <v>2424</v>
       </c>
@@ -31475,7 +31484,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="193" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A193" s="36" t="s">
         <v>1527</v>
       </c>
@@ -31597,7 +31606,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="194" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A194" s="36" t="s">
         <v>1642</v>
       </c>
@@ -31721,7 +31730,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="195" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A195" s="27" t="s">
         <v>1649</v>
       </c>
@@ -31843,7 +31852,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="196" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A196" s="27" t="s">
         <v>1741</v>
       </c>
@@ -31965,7 +31974,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="197" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A197" s="36" t="s">
         <v>1767</v>
       </c>
@@ -32089,7 +32098,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="198" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A198" s="27" t="s">
         <v>1930</v>
       </c>
@@ -32211,7 +32220,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="199" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A199" s="27" t="s">
         <v>1937</v>
       </c>
@@ -32333,7 +32342,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="200" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A200" s="27" t="s">
         <v>2058</v>
       </c>
@@ -32457,7 +32466,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="201" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A201" s="36" t="s">
         <v>2373</v>
       </c>
@@ -32579,7 +32588,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="202" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A202" s="27" t="s">
         <v>2385</v>
       </c>
@@ -32701,7 +32710,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="203" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A203" s="36" t="s">
         <v>2473</v>
       </c>
@@ -32823,7 +32832,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="204" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A204" s="12" t="s">
         <v>641</v>
       </c>
@@ -32943,7 +32952,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="205" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A205" s="3" t="s">
         <v>647</v>
       </c>
@@ -33061,7 +33070,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="206" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A206" s="24" t="s">
         <v>1343</v>
       </c>
@@ -33183,7 +33192,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="207" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A207" s="27" t="s">
         <v>1540</v>
       </c>
@@ -33305,7 +33314,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="208" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A208" s="12" t="s">
         <v>653</v>
       </c>
@@ -33425,7 +33434,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="209" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A209" s="36" t="s">
         <v>1783</v>
       </c>
@@ -33547,7 +33556,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="210" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A210" s="24" t="s">
         <v>1343</v>
       </c>
@@ -33669,7 +33678,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="211" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A211" s="3" t="s">
         <v>660</v>
       </c>
@@ -33787,7 +33796,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="212" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A212" s="24" t="s">
         <v>1128</v>
       </c>
@@ -33905,7 +33914,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="213" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A213" s="36" t="s">
         <v>1140</v>
       </c>
@@ -34023,7 +34032,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="214" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A214" s="36" t="s">
         <v>1555</v>
       </c>
@@ -34147,7 +34156,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="215" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A215" s="27" t="s">
         <v>2553</v>
       </c>
@@ -34269,7 +34278,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="216" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A216" s="12" t="s">
         <v>712</v>
       </c>
@@ -34389,7 +34398,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="217" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A217" s="3" t="s">
         <v>726</v>
       </c>
@@ -34509,7 +34518,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="218" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A218" s="12" t="s">
         <v>1220</v>
       </c>
@@ -34623,7 +34632,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="219" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A219" s="3" t="s">
         <v>1265</v>
       </c>
@@ -34739,7 +34748,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="220" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A220" s="12" t="s">
         <v>986</v>
       </c>
@@ -34855,7 +34864,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="221" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A221" s="3" t="s">
         <v>1218</v>
       </c>
@@ -34971,7 +34980,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="222" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A222" s="24" t="s">
         <v>754</v>
       </c>
@@ -35087,7 +35096,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="223" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A223" s="24" t="s">
         <v>761</v>
       </c>
@@ -35203,7 +35212,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="224" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A224" s="24" t="s">
         <v>763</v>
       </c>
@@ -35319,7 +35328,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="225" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A225" s="24" t="s">
         <v>765</v>
       </c>
@@ -35435,7 +35444,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="226" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A226" s="3" t="s">
         <v>320</v>
       </c>
@@ -35557,7 +35566,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="227" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A227" s="24" t="s">
         <v>754</v>
       </c>
@@ -35675,7 +35684,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="228" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A228" s="24" t="s">
         <v>761</v>
       </c>
@@ -35793,7 +35802,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="229" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A229" s="24" t="s">
         <v>763</v>
       </c>
@@ -35911,7 +35920,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="230" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A230" s="24" t="s">
         <v>765</v>
       </c>
@@ -36029,7 +36038,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="231" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A231" s="3" t="s">
         <v>400</v>
       </c>
@@ -36149,7 +36158,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="232" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A232" s="24" t="s">
         <v>754</v>
       </c>
@@ -36267,7 +36276,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="233" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A233" s="24" t="s">
         <v>761</v>
       </c>
@@ -36385,7 +36394,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="234" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A234" s="24" t="s">
         <v>763</v>
       </c>
@@ -36503,7 +36512,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="235" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A235" s="24" t="s">
         <v>765</v>
       </c>
@@ -36621,7 +36630,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="236" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A236" s="21" t="s">
         <v>268</v>
       </c>
@@ -36741,7 +36750,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="237" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A237" s="24" t="s">
         <v>754</v>
       </c>
@@ -36859,7 +36868,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="238" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A238" s="24" t="s">
         <v>761</v>
       </c>
@@ -36977,7 +36986,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="239" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A239" s="24" t="s">
         <v>763</v>
       </c>
@@ -37095,7 +37104,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="240" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A240" s="24" t="s">
         <v>765</v>
       </c>
@@ -37213,7 +37222,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="241" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A241" s="12" t="s">
         <v>288</v>
       </c>
@@ -37333,7 +37342,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="242" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A242" s="24" t="s">
         <v>754</v>
       </c>
@@ -37451,7 +37460,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="243" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A243" s="24" t="s">
         <v>761</v>
       </c>
@@ -37569,7 +37578,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="244" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A244" s="24" t="s">
         <v>763</v>
       </c>
@@ -37687,7 +37696,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="245" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A245" s="24" t="s">
         <v>765</v>
       </c>
@@ -37805,7 +37814,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="246" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A246" s="21" t="s">
         <v>435</v>
       </c>
@@ -37925,7 +37934,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="247" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A247" s="24" t="s">
         <v>754</v>
       </c>
@@ -38043,7 +38052,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="248" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A248" s="24" t="s">
         <v>761</v>
       </c>
@@ -38161,7 +38170,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="249" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A249" s="24" t="s">
         <v>763</v>
       </c>
@@ -38279,7 +38288,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="250" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A250" s="24" t="s">
         <v>765</v>
       </c>
@@ -38397,7 +38406,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="251" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A251" s="12" t="s">
         <v>719</v>
       </c>
@@ -38517,7 +38526,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="252" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A252" s="3" t="s">
         <v>831</v>
       </c>
@@ -38631,7 +38640,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="253" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A253" s="21" t="s">
         <v>1016</v>
       </c>
@@ -38747,7 +38756,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="254" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A254" s="24" t="s">
         <v>1002</v>
       </c>
@@ -38865,7 +38874,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="255" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A255" s="36" t="s">
         <v>2065</v>
       </c>
@@ -38987,7 +38996,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="256" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A256" s="36" t="s">
         <v>2361</v>
       </c>
@@ -39109,7 +39118,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="257" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A257" s="27" t="s">
         <v>2366</v>
       </c>
@@ -39231,7 +39240,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="258" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A258" s="21" t="s">
         <v>268</v>
       </c>
@@ -39351,7 +39360,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="259" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A259" s="3" t="s">
         <v>305</v>
       </c>
@@ -39471,7 +39480,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="260" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A260" s="27" t="s">
         <v>2253</v>
       </c>
@@ -39595,7 +39604,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="261" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A261" s="27" t="s">
         <v>775</v>
       </c>
@@ -39713,7 +39722,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="262" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A262" s="3" t="s">
         <v>983</v>
       </c>
@@ -39831,7 +39840,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="263" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A263" s="36" t="s">
         <v>991</v>
       </c>
@@ -39951,7 +39960,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="264" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A264" s="24" t="s">
         <v>1002</v>
       </c>
@@ -40069,7 +40078,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="265" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A265" s="3" t="s">
         <v>1058</v>
       </c>
@@ -40193,7 +40202,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="266" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A266" s="3" t="s">
         <v>1083</v>
       </c>
@@ -40315,7 +40324,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="267" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A267" s="3" t="s">
         <v>1101</v>
       </c>
@@ -40439,7 +40448,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="268" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A268" s="3" t="s">
         <v>1121</v>
       </c>
@@ -40563,7 +40572,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="269" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A269" s="3" t="s">
         <v>1255</v>
       </c>
@@ -40685,7 +40694,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="270" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A270" s="24" t="s">
         <v>1311</v>
       </c>
@@ -40801,7 +40810,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="271" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A271" s="12" t="s">
         <v>1334</v>
       </c>
@@ -40925,7 +40934,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="272" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A272" s="27" t="s">
         <v>1402</v>
       </c>
@@ -41047,7 +41056,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="273" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A273" s="36" t="s">
         <v>1547</v>
       </c>
@@ -41167,7 +41176,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="274" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A274" s="36" t="s">
         <v>1076</v>
       </c>
@@ -41283,7 +41292,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="275" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A275" s="36" t="s">
         <v>1882</v>
       </c>
@@ -41405,7 +41414,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="276" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A276" s="36" t="s">
         <v>2072</v>
       </c>
@@ -41527,7 +41536,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="277" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A277" s="36" t="s">
         <v>2110</v>
       </c>
@@ -41649,7 +41658,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="278" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A278" s="36" t="s">
         <v>2117</v>
       </c>
@@ -41771,7 +41780,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="279" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A279" s="36" t="s">
         <v>2466</v>
       </c>
@@ -41893,7 +41902,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="280" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A280" s="21" t="s">
         <v>435</v>
       </c>
@@ -42013,7 +42022,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="281" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A281" s="12" t="s">
         <v>442</v>
       </c>
@@ -42133,7 +42142,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="282" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A282" s="36" t="s">
         <v>1572</v>
       </c>
@@ -42255,7 +42264,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="283" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A283" s="36" t="s">
         <v>1703</v>
       </c>
@@ -42377,7 +42386,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="284" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A284" s="27" t="s">
         <v>1791</v>
       </c>
@@ -42499,7 +42508,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="285" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A285" s="27" t="s">
         <v>1917</v>
       </c>
@@ -42623,7 +42632,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="286" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A286" s="36" t="s">
         <v>2330</v>
       </c>
@@ -42745,7 +42754,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="287" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A287" s="36" t="s">
         <v>2480</v>
       </c>
@@ -42867,7 +42876,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="288" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A288" s="12" t="s">
         <v>331</v>
       </c>
@@ -42987,7 +42996,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="289" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A289" s="3" t="s">
         <v>560</v>
       </c>
@@ -43107,7 +43116,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="290" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A290" s="21" t="s">
         <v>135</v>
       </c>
@@ -43229,7 +43238,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="291" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A291" s="3" t="s">
         <v>368</v>
       </c>
@@ -43351,7 +43360,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="292" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A292" s="24" t="s">
         <v>781</v>
       </c>
@@ -43469,7 +43478,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="293" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A293" s="24" t="s">
         <v>786</v>
       </c>
@@ -43587,7 +43596,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="294" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A294" s="24" t="s">
         <v>781</v>
       </c>
@@ -43705,7 +43714,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="295" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A295" s="24" t="s">
         <v>786</v>
       </c>
@@ -43823,7 +43832,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="296" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A296" s="12" t="s">
         <v>549</v>
       </c>
@@ -43945,7 +43954,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="297" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A297" s="24" t="s">
         <v>781</v>
       </c>
@@ -44063,7 +44072,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="298" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A298" s="27" t="s">
         <v>778</v>
       </c>
@@ -44181,7 +44190,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="299" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A299" s="24" t="s">
         <v>781</v>
       </c>
@@ -44299,7 +44308,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="300" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A300" s="24" t="s">
         <v>786</v>
       </c>
@@ -44417,7 +44426,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="301" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A301" s="21" t="s">
         <v>1128</v>
       </c>
@@ -44531,7 +44540,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="302" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A302" s="36" t="s">
         <v>1000</v>
       </c>
@@ -44649,7 +44658,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="303" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A303" s="21" t="s">
         <v>1128</v>
       </c>
@@ -44763,7 +44772,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="304" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A304" s="27" t="s">
         <v>988</v>
       </c>
@@ -44879,7 +44888,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="305" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A305" s="12" t="s">
         <v>1216</v>
       </c>
@@ -44995,7 +45004,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="306" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A306" s="36" t="s">
         <v>2148</v>
       </c>
@@ -45111,7 +45120,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="307" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A307" s="24" t="s">
         <v>1191</v>
       </c>
@@ -45231,7 +45240,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="308" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A308" s="24" t="s">
         <v>1199</v>
       </c>
@@ -45349,7 +45358,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="309" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A309" s="24" t="s">
         <v>1201</v>
       </c>
@@ -45467,7 +45476,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="310" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A310" s="24" t="s">
         <v>1203</v>
       </c>
@@ -45585,7 +45594,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="311" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A311" s="27" t="s">
         <v>2190</v>
       </c>
@@ -45707,7 +45716,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="312" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A312" s="12" t="s">
         <v>801</v>
       </c>
@@ -45829,7 +45838,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="313" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A313" s="27" t="s">
         <v>1168</v>
       </c>
@@ -45949,7 +45958,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="314" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A314" s="3" t="s">
         <v>1446</v>
       </c>
@@ -46073,7 +46082,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="315" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A315" s="12" t="s">
         <v>162</v>
       </c>
@@ -46193,7 +46202,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="316" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A316" s="12" t="s">
         <v>499</v>
       </c>
@@ -46313,7 +46322,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="317" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A317" s="3" t="s">
         <v>528</v>
       </c>
@@ -46433,7 +46442,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="318" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A318" s="21" t="s">
         <v>994</v>
       </c>
@@ -46549,7 +46558,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="319" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A319" s="21" t="s">
         <v>52</v>
       </c>
@@ -46669,7 +46678,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="320" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A320" s="3" t="s">
         <v>1133</v>
       </c>
@@ -46785,7 +46794,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="321" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A321" s="21" t="s">
         <v>994</v>
       </c>
@@ -46901,7 +46910,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="322" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A322" s="21" t="s">
         <v>52</v>
       </c>
@@ -47021,7 +47030,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="323" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A323" s="21" t="s">
         <v>994</v>
       </c>
@@ -47135,7 +47144,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="324" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A324" s="21" t="s">
         <v>52</v>
       </c>
@@ -47255,7 +47264,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="325" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A325" s="12" t="s">
         <v>360</v>
       </c>
@@ -47375,7 +47384,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="326" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A326" s="12" t="s">
         <v>427</v>
       </c>
@@ -47495,7 +47504,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="327" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A327" s="12" t="s">
         <v>344</v>
       </c>
@@ -47615,7 +47624,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="328" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A328" s="27" t="s">
         <v>932</v>
       </c>
@@ -47733,7 +47742,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="329" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A329" s="24" t="s">
         <v>954</v>
       </c>
@@ -47851,7 +47860,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="330" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A330" s="24" t="s">
         <v>978</v>
       </c>
@@ -47969,7 +47978,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="331" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A331" s="24" t="s">
         <v>1114</v>
       </c>
@@ -48093,7 +48102,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="332" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A332" s="12" t="s">
         <v>418</v>
       </c>
@@ -48213,7 +48222,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="333" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A333" s="24" t="s">
         <v>1324</v>
       </c>
@@ -48333,7 +48342,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="334" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A334" s="36" t="s">
         <v>947</v>
       </c>
@@ -48451,7 +48460,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="335" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A335" s="24" t="s">
         <v>960</v>
       </c>
@@ -48569,7 +48578,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="336" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A336" s="24" t="s">
         <v>970</v>
       </c>
@@ -48687,7 +48696,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="337" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A337" s="24" t="s">
         <v>972</v>
       </c>
@@ -48805,7 +48814,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="338" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A338" s="12" t="s">
         <v>1286</v>
       </c>
@@ -48923,7 +48932,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="339" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A339" s="3" t="s">
         <v>1317</v>
       </c>
@@ -49041,7 +49050,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="340" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A340" s="12" t="s">
         <v>520</v>
       </c>
@@ -49161,7 +49170,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="341" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A341" s="3" t="s">
         <v>1597</v>
       </c>
@@ -49279,7 +49288,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="342" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A342" s="12" t="s">
         <v>573</v>
       </c>
@@ -49399,7 +49408,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="343" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A343" s="12" t="s">
         <v>606</v>
       </c>
@@ -49519,7 +49528,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="344" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A344" s="12" t="s">
         <v>1868</v>
       </c>
@@ -49637,7 +49646,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="345" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A345" s="3" t="s">
         <v>1875</v>
       </c>
@@ -49755,7 +49764,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="346" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A346" s="3" t="s">
         <v>1893</v>
       </c>
@@ -49873,7 +49882,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="347" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A347" s="3" t="s">
         <v>2182</v>
       </c>
@@ -49991,7 +50000,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="348" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A348" s="36" t="s">
         <v>1473</v>
       </c>
@@ -50111,7 +50120,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="349" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A349" s="27" t="s">
         <v>1579</v>
       </c>
@@ -50231,7 +50240,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="350" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A350" s="36" t="s">
         <v>1945</v>
       </c>
@@ -50351,7 +50360,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="351" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A351" s="27" t="s">
         <v>1952</v>
       </c>
@@ -50471,7 +50480,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="352" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A352" s="36" t="s">
         <v>2035</v>
       </c>
@@ -50591,7 +50600,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="353" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A353" s="36" t="s">
         <v>2079</v>
       </c>
@@ -50711,7 +50720,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="354" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A354" s="27" t="s">
         <v>2123</v>
       </c>
@@ -50831,7 +50840,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="355" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A355" s="3" t="s">
         <v>1206</v>
       </c>
@@ -50955,7 +50964,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="356" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A356" s="27" t="s">
         <v>1352</v>
       </c>
@@ -51081,7 +51090,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="357" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A357" s="36" t="s">
         <v>1362</v>
       </c>
@@ -51207,7 +51216,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="358" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A358" s="27" t="s">
         <v>1369</v>
       </c>
@@ -51333,7 +51342,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="359" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A359" s="36" t="s">
         <v>1377</v>
       </c>
@@ -51459,7 +51468,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="360" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A360" s="27" t="s">
         <v>1386</v>
       </c>
@@ -51585,7 +51594,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="361" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A361" s="36" t="s">
         <v>1394</v>
       </c>
@@ -51711,7 +51720,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="362" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A362" s="36" t="s">
         <v>2022</v>
       </c>
@@ -51831,7 +51840,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="363" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A363" s="27" t="s">
         <v>2105</v>
       </c>
@@ -51951,7 +51960,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="364" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A364" s="27" t="s">
         <v>2430</v>
       </c>
@@ -52073,7 +52082,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="365" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A365" s="36" t="s">
         <v>2432</v>
       </c>
@@ -52193,7 +52202,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="366" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A366" s="27" t="s">
         <v>2434</v>
       </c>
@@ -52313,7 +52322,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="367" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A367" s="36" t="s">
         <v>2436</v>
       </c>
@@ -52435,7 +52444,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="368" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A368" s="27" t="s">
         <v>2442</v>
       </c>
@@ -52555,7 +52564,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="369" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A369" s="36" t="s">
         <v>2444</v>
       </c>
@@ -52677,7 +52686,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="370" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A370" s="36" t="s">
         <v>2527</v>
       </c>
@@ -52797,7 +52806,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="371" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A371" s="3" t="s">
         <v>698</v>
       </c>
@@ -52917,7 +52926,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="372" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A372" s="12" t="s">
         <v>739</v>
       </c>
@@ -53037,7 +53046,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="373" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A373" s="12" t="s">
         <v>746</v>
       </c>
@@ -53157,7 +53166,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="374" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A374" s="3" t="s">
         <v>194</v>
       </c>
@@ -53279,7 +53288,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="375" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A375" s="3" t="s">
         <v>298</v>
       </c>
@@ -53399,7 +53408,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="376" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A376" s="12" t="s">
         <v>597</v>
       </c>
@@ -53519,7 +53528,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="377" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A377" s="12" t="s">
         <v>668</v>
       </c>
@@ -53639,7 +53648,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="378" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A378" s="3" t="s">
         <v>674</v>
       </c>
@@ -53759,7 +53768,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="379" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A379" s="3" t="s">
         <v>705</v>
       </c>
@@ -53879,7 +53888,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="380" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A380" s="12" t="s">
         <v>230</v>
       </c>
@@ -53999,7 +54008,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="381" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A381" s="12" t="s">
         <v>352</v>
       </c>
@@ -54119,7 +54128,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="382" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A382" s="3" t="s">
         <v>483</v>
       </c>
@@ -54239,7 +54248,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="383" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A383" s="21" t="s">
         <v>183</v>
       </c>
@@ -54359,7 +54368,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="384" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A384" s="21" t="s">
         <v>238</v>
       </c>
@@ -54479,7 +54488,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="385" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A385" s="21" t="s">
         <v>250</v>
       </c>
@@ -54599,7 +54608,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="386" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A386" s="21" t="s">
         <v>411</v>
       </c>
@@ -54719,7 +54728,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="387" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A387" s="21" t="s">
         <v>567</v>
       </c>
@@ -54839,7 +54848,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="388" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A388" s="3" t="s">
         <v>151</v>
       </c>
@@ -54957,7 +54966,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="389" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A389" s="12" t="s">
         <v>535</v>
       </c>
@@ -55079,7 +55088,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="390" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A390" s="12" t="s">
         <v>581</v>
       </c>
@@ -55199,7 +55208,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="391" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A391" s="3" t="s">
         <v>620</v>
       </c>
@@ -55319,7 +55328,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="392" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A392" s="21" t="s">
         <v>994</v>
       </c>
@@ -55435,7 +55444,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="393" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A393" s="24" t="s">
         <v>944</v>
       </c>
@@ -55555,7 +55564,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="394" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A394" s="36" t="s">
         <v>956</v>
       </c>
@@ -55673,7 +55682,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="395" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A395" s="21" t="s">
         <v>52</v>
       </c>
@@ -55793,7 +55802,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="396" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A396" s="27" t="s">
         <v>1029</v>
       </c>
@@ -55911,7 +55920,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="397" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A397" s="36" t="s">
         <v>1034</v>
       </c>
@@ -56029,7 +56038,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="398" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A398" s="36" t="s">
         <v>1050</v>
       </c>
@@ -56149,7 +56158,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="399" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A399" s="24" t="s">
         <v>1095</v>
       </c>
@@ -56269,7 +56278,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="400" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A400" s="21" t="s">
         <v>277</v>
       </c>
@@ -56389,7 +56398,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="401" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A401" s="27" t="s">
         <v>1183</v>
       </c>
@@ -56509,7 +56518,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="402" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A402" s="21" t="s">
         <v>277</v>
       </c>
@@ -56629,7 +56638,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="403" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A403" s="21" t="s">
         <v>52</v>
       </c>
@@ -56749,7 +56758,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="404" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A404" s="24" t="s">
         <v>1324</v>
       </c>
@@ -56869,7 +56878,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="405" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A405" s="24" t="s">
         <v>1304</v>
       </c>
@@ -56989,7 +56998,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="406" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A406" s="24" t="s">
         <v>1341</v>
       </c>
@@ -57109,7 +57118,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="407" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A407" s="36" t="s">
         <v>1466</v>
       </c>
@@ -57231,7 +57240,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="408" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A408" s="36" t="s">
         <v>2128</v>
       </c>
@@ -57353,7 +57362,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="409" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A409" s="27" t="s">
         <v>2134</v>
       </c>
@@ -57475,7 +57484,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="410" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A410" s="36" t="s">
         <v>2240</v>
       </c>
@@ -57599,7 +57608,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="411" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A411" s="36" t="s">
         <v>1005</v>
       </c>
@@ -57719,7 +57728,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="412" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A412" s="3" t="s">
         <v>1014</v>
       </c>
@@ -57839,7 +57848,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="413" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A413" s="27" t="s">
         <v>1843</v>
       </c>
@@ -57961,7 +57970,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="414" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A414" s="36" t="s">
         <v>2261</v>
       </c>
@@ -58083,7 +58092,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="415" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A415" s="36" t="s">
         <v>2316</v>
       </c>
@@ -58205,7 +58214,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="416" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A416" s="27" t="s">
         <v>2392</v>
       </c>
@@ -58327,7 +58336,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="417" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A417" s="27" t="s">
         <v>2398</v>
       </c>
@@ -58449,7 +58458,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="418" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A418" s="27" t="s">
         <v>2486</v>
       </c>
@@ -58571,7 +58580,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="419" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A419" s="3" t="s">
         <v>88</v>
       </c>
@@ -58691,7 +58700,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="420" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A420" s="12" t="s">
         <v>204</v>
       </c>
@@ -58811,7 +58820,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="421" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A421" s="21" t="s">
         <v>960</v>
       </c>
@@ -58927,7 +58936,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="422" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A422" s="12" t="s">
         <v>1176</v>
       </c>
@@ -59045,7 +59054,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="423" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A423" s="12" t="s">
         <v>1185</v>
       </c>
@@ -59163,7 +59172,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="424" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A424" s="12" t="s">
         <v>102</v>
       </c>
@@ -59283,7 +59292,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="425" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A425" s="3" t="s">
         <v>589</v>
       </c>
@@ -59403,7 +59412,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="426" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A426" s="21" t="s">
         <v>183</v>
       </c>
@@ -59523,7 +59532,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="427" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A427" s="27" t="s">
         <v>1861</v>
       </c>
@@ -59645,7 +59654,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="428" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A428" s="21" t="s">
         <v>238</v>
       </c>
@@ -59765,7 +59774,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="429" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A429" s="21" t="s">
         <v>250</v>
       </c>
@@ -59885,7 +59894,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="430" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A430" s="24" t="s">
         <v>1036</v>
       </c>
@@ -60003,7 +60012,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="431" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A431" s="21" t="s">
         <v>411</v>
       </c>
@@ -60123,7 +60132,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="432" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A432" s="21" t="s">
         <v>567</v>
       </c>
@@ -60243,7 +60252,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="433" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A433" s="36" t="s">
         <v>2337</v>
       </c>
@@ -60365,7 +60374,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="434" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A434" s="12" t="s">
         <v>867</v>
       </c>
@@ -60485,7 +60494,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="435" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A435" s="36" t="s">
         <v>2506</v>
       </c>
@@ -60607,7 +60616,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="436" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A436" s="21" t="s">
         <v>872</v>
       </c>
@@ -60727,7 +60736,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="437" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A437" s="3" t="s">
         <v>874</v>
       </c>
@@ -60847,7 +60856,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="438" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A438" s="36" t="s">
         <v>1824</v>
       </c>
@@ -60969,7 +60978,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="439" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A439" s="36" t="s">
         <v>2405</v>
       </c>
@@ -61091,7 +61100,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="440" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A440" s="27" t="s">
         <v>2539</v>
       </c>
@@ -61213,7 +61222,7 @@
         <v>2546</v>
       </c>
     </row>
-    <row r="441" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A441" s="27" t="s">
         <v>2566</v>
       </c>
@@ -61335,7 +61344,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="442" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A442" s="24" t="s">
         <v>1304</v>
       </c>
@@ -61455,7 +61464,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="443" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A443" s="24" t="s">
         <v>1324</v>
       </c>
@@ -61575,7 +61584,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="444" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A444" s="24" t="s">
         <v>1618</v>
       </c>
@@ -61697,7 +61706,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="445" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A445" s="27" t="s">
         <v>1696</v>
       </c>
@@ -61819,7 +61828,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="446" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A446" s="27" t="s">
         <v>1754</v>
       </c>
@@ -61941,7 +61950,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="447" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A447" s="36" t="s">
         <v>2547</v>
       </c>
@@ -62061,7 +62070,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="448" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A448" s="36" t="s">
         <v>2584</v>
       </c>
@@ -62183,7 +62192,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="449" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A449" s="21" t="s">
         <v>880</v>
       </c>
@@ -62303,7 +62312,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="450" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A450" s="12" t="s">
         <v>886</v>
       </c>
@@ -62423,7 +62432,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="451" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A451" s="21" t="s">
         <v>890</v>
       </c>
@@ -62543,7 +62552,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="452" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A452" s="27" t="s">
         <v>2356</v>
       </c>
@@ -62663,7 +62672,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="453" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A453" s="24" t="s">
         <v>1304</v>
       </c>
@@ -62783,7 +62792,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="454" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A454" s="24" t="s">
         <v>1341</v>
       </c>
@@ -62903,7 +62912,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="455" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A455" s="36" t="s">
         <v>2198</v>
       </c>
@@ -63025,7 +63034,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="456" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A456" s="24" t="s">
         <v>1304</v>
       </c>
@@ -63145,7 +63154,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="457" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A457" s="27" t="s">
         <v>1804</v>
       </c>
@@ -63265,7 +63274,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="458" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A458" s="24" t="s">
         <v>1304</v>
       </c>
@@ -63385,7 +63394,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="459" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A459" s="21" t="s">
         <v>892</v>
       </c>
@@ -63505,7 +63514,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="460" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A460" s="24" t="s">
         <v>1625</v>
       </c>
@@ -63625,7 +63634,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="461" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A461" s="24" t="s">
         <v>1625</v>
       </c>
@@ -63747,7 +63756,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="462" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A462" s="24" t="s">
         <v>1341</v>
       </c>
@@ -63867,7 +63876,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="463" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A463" s="36" t="s">
         <v>1418</v>
       </c>
@@ -63987,7 +63996,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="464" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A464" s="24" t="s">
         <v>1618</v>
       </c>
@@ -64109,7 +64118,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="465" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A465" s="36" t="s">
         <v>1855</v>
       </c>
@@ -64229,7 +64238,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="466" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A466" s="24" t="s">
         <v>2323</v>
       </c>
@@ -64351,7 +64360,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="467" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A467" s="27" t="s">
         <v>2533</v>
       </c>
@@ -64473,7 +64482,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="468" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A468" s="21" t="s">
         <v>896</v>
       </c>
@@ -64593,7 +64602,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="469" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A469" s="21" t="s">
         <v>903</v>
       </c>
@@ -64713,7 +64722,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="470" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A470" s="21" t="s">
         <v>910</v>
       </c>
@@ -64833,7 +64842,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="471" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A471" s="21" t="s">
         <v>913</v>
       </c>
@@ -64949,7 +64958,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="472" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A472" s="24" t="s">
         <v>1036</v>
       </c>
@@ -65067,7 +65076,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="473" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A473" s="21" t="s">
         <v>920</v>
       </c>
@@ -65187,7 +65196,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="474" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A474" s="21" t="s">
         <v>930</v>
       </c>
@@ -65307,7 +65316,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="475" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A475" s="27" t="s">
         <v>844</v>
       </c>
@@ -65429,7 +65438,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="476" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A476" s="36" t="s">
         <v>847</v>
       </c>
@@ -65553,7 +65562,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="477" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A477" s="24" t="s">
         <v>1304</v>
       </c>
@@ -65673,7 +65682,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="478" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A478" s="24" t="s">
         <v>1324</v>
       </c>
@@ -65793,7 +65802,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="479" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A479" s="27" t="s">
         <v>2411</v>
       </c>
@@ -65915,7 +65924,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="480" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A480" s="36" t="s">
         <v>2493</v>
       </c>
@@ -66037,7 +66046,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="481" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A481" s="36" t="s">
         <v>2579</v>
       </c>
@@ -66157,7 +66166,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="482" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A482" s="21" t="s">
         <v>1016</v>
       </c>
@@ -66273,7 +66282,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="483" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A483" s="12" t="s">
         <v>789</v>
       </c>
@@ -66393,7 +66402,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="484" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A484" s="3" t="s">
         <v>794</v>
       </c>
@@ -66513,7 +66522,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="485" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A485" s="3" t="s">
         <v>75</v>
       </c>
@@ -66633,7 +66642,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="486" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A486" s="3" t="s">
         <v>808</v>
       </c>
@@ -66753,7 +66762,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="487" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A487" s="12" t="s">
         <v>810</v>
       </c>
@@ -66875,7 +66884,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="488" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A488" s="12" t="s">
         <v>115</v>
       </c>
@@ -66995,7 +67004,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="489" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A489" s="23"/>
       <c r="B489" s="23"/>
       <c r="C489" s="23"/>
